--- a/IGR_REF/Data/Documents/Config.xlsx
+++ b/IGR_REF/Data/Documents/Config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="97">
   <si>
     <t>Name</t>
   </si>
@@ -112,6 +112,12 @@
     <t>https://gras.mahakosh.gov.in/echallan/igr/</t>
   </si>
   <si>
+    <t>GRNPageURL2</t>
+  </si>
+  <si>
+    <t>https://gras.mahakosh.gov.in/echallan/igr/challan/</t>
+  </si>
+  <si>
     <t>DHCPageURL</t>
   </si>
   <si>
@@ -145,16 +151,22 @@
     <t>Swapna@123</t>
   </si>
   <si>
-    <t>newTenant</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>ChallanUserName</t>
+  </si>
+  <si>
+    <t>laxmanigr</t>
+  </si>
+  <si>
+    <t>ChallanPassword</t>
+  </si>
+  <si>
+    <t>N@41909i</t>
   </si>
   <si>
     <t>Registration</t>
   </si>
   <si>
-    <t>DHC</t>
+    <t>DHCAmount</t>
   </si>
   <si>
     <t>ComplaintEmail</t>
@@ -1273,7 +1285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z988"/>
+  <dimension ref="A1:Z990"/>
   <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5714285714286" customWidth="1"/>
@@ -1454,7 +1466,7 @@
       <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1462,7 +1474,7 @@
       <c r="A19" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1474,116 +1486,130 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1" spans="1:2">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1" spans="1:2">
-      <c r="A24" t="s">
+    <row r="21" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="2">
-        <v>9011092282</v>
-      </c>
-    </row>
+      <c r="B21" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1"/>
     <row r="25" ht="14.25" customHeight="1" spans="1:2">
       <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1" spans="1:2">
-      <c r="A27" t="s">
+      <c r="B25" s="2">
+        <v>9011092282</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A26" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="29" ht="14.25" customHeight="1" spans="1:2">
       <c r="A29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1" spans="1:2">
-      <c r="A30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="2">
-        <v>300</v>
-      </c>
-    </row>
+        <v>42</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1"/>
     <row r="31" ht="14.25" customHeight="1" spans="1:2">
       <c r="A31" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="B31" s="2">
+        <v>1000</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:2">
       <c r="A32" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1" spans="2:2">
-      <c r="B35" t="s">
+      <c r="B32" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A33" t="s">
         <v>46</v>
       </c>
-    </row>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1"/>
     <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A38" t="s">
+    <row r="37" ht="14.25" customHeight="1" spans="2:2">
+      <c r="B37" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" t="s">
+    </row>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1" spans="1:3">
+      <c r="A39" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1"/>
+      <c r="B39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:3">
       <c r="A40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B40" s="7"/>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1" spans="1:3">
+      <c r="A42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" t="s">
+        <v>58</v>
+      </c>
+    </row>
     <row r="43" ht="14.25" customHeight="1"/>
     <row r="44" ht="14.25" customHeight="1"/>
     <row r="45" ht="14.25" customHeight="1"/>
@@ -2530,6 +2556,8 @@
     <row r="986" ht="14.25" customHeight="1"/>
     <row r="987" ht="14.25" customHeight="1"/>
     <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2585,143 +2613,143 @@
     </row>
     <row r="2" ht="30" spans="1:3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="45" spans="1:3">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1" spans="1:3">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>
     <row r="7" ht="14.25" customHeight="1" spans="1:3">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:3">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:3">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:3">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:3">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:3">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1"/>
     <row r="14" ht="14.25" customHeight="1" spans="1:3">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:3">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="30" spans="1:3">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:2">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -2729,7 +2757,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:2">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -2737,7 +2765,7 @@
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B20">
         <v>1.5</v>
@@ -2745,10 +2773,10 @@
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B21">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1"/>
@@ -3741,13 +3769,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>

--- a/IGR_REF/Data/Documents/Config.xlsx
+++ b/IGR_REF/Data/Documents/Config.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="105">
   <si>
     <t>Name</t>
   </si>
@@ -46,6 +46,12 @@
     <t>https://efilingigr.maharashtra.gov.in/ereg/</t>
   </si>
   <si>
+    <t>PVPage</t>
+  </si>
+  <si>
+    <t>frmPoliceVerification.aspx</t>
+  </si>
+  <si>
     <t>DocsPath</t>
   </si>
   <si>
@@ -58,6 +64,9 @@
     <t>C:\Users\laxma\Downloads</t>
   </si>
   <si>
+    <t>https://efilingigr.maharashtra.gov.in/ereg/frmPoliceVerification.aspx</t>
+  </si>
+  <si>
     <t>DataEntryFileName</t>
   </si>
   <si>
@@ -100,12 +109,24 @@
     <t>IdentifierDetails</t>
   </si>
   <si>
+    <t>FamilyDetailsSheet</t>
+  </si>
+  <si>
+    <t>FamilyDetails</t>
+  </si>
+  <si>
     <t>ChallanDetailsSheet</t>
   </si>
   <si>
     <t>ChallanDetails</t>
   </si>
   <si>
+    <t>PVDetailsSheet</t>
+  </si>
+  <si>
+    <t>PVDetails</t>
+  </si>
+  <si>
     <t>GRNPageURL</t>
   </si>
   <si>
@@ -311,6 +332,9 @@
   </si>
   <si>
     <t>Delay</t>
+  </si>
+  <si>
+    <t>DelayPayment</t>
   </si>
   <si>
     <t>Asset</t>
@@ -1285,7 +1309,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z990"/>
+  <dimension ref="A1:Z992"/>
   <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5714285714286" customWidth="1"/>
@@ -1337,8 +1361,12 @@
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:26">
-      <c r="A3" s="1"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1366,252 +1394,270 @@
     </row>
     <row r="4" ht="14.25" customHeight="1" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" spans="2:2">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:2">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:2">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:2">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:2">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:2">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:2">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1" spans="1:2">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1" spans="1:2">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:2">
       <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:2">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:2">
       <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1"/>
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:2">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>
     <row r="25" ht="14.25" customHeight="1" spans="1:2">
       <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="2">
+        <v>42</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="2">
         <v>9011092282</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1" spans="1:2">
-      <c r="A26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1"/>
     <row r="28" ht="14.25" customHeight="1" spans="1:2">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1" spans="1:2">
-      <c r="A29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:2">
       <c r="A31" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1" spans="1:2">
-      <c r="A32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="2">
-        <v>300</v>
-      </c>
-    </row>
+        <v>49</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1" spans="1:2">
       <c r="A33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1000</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:2">
       <c r="A34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1" spans="2:2">
-      <c r="B37" t="s">
-        <v>50</v>
-      </c>
-    </row>
+        <v>52</v>
+      </c>
+      <c r="B34" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1"/>
     <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="7"/>
-      <c r="C40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1" spans="2:2">
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1" spans="1:3">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
+        <v>60</v>
+      </c>
+    </row>
     <row r="42" ht="14.25" customHeight="1" spans="1:3">
       <c r="A42" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>57</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B42" s="7"/>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1" spans="1:3">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="45" ht="14.25" customHeight="1"/>
     <row r="46" ht="14.25" customHeight="1"/>
     <row r="47" ht="14.25" customHeight="1"/>
@@ -2558,6 +2604,8 @@
     <row r="988" ht="14.25" customHeight="1"/>
     <row r="989" ht="14.25" customHeight="1"/>
     <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2613,143 +2661,143 @@
     </row>
     <row r="2" ht="30" spans="1:3">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="45" spans="1:3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1" spans="1:3">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>
     <row r="7" ht="14.25" customHeight="1" spans="1:3">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:3">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:3">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:3">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:3">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:3">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1"/>
     <row r="14" ht="14.25" customHeight="1" spans="1:3">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:3">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="30" spans="1:3">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:2">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -2757,7 +2805,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:2">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -2765,7 +2813,7 @@
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:2">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B20">
         <v>1.5</v>
@@ -2773,13 +2821,20 @@
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:2">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1" spans="1:2">
+      <c r="A22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+    </row>
     <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1"/>
     <row r="25" ht="14.25" customHeight="1"/>
@@ -3769,13 +3824,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
